--- a/warehouse/templates/export_file/dropshipping_packing_list_template.xlsx
+++ b/warehouse/templates/export_file/dropshipping_packing_list_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
   <si>
     <t>唛头</t>
   </si>
@@ -63,28 +63,28 @@
     <t>仓库/私人 地址</t>
   </si>
   <si>
+    <t>派送方式</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>仓库代码</t>
+  </si>
+  <si>
     <t>FBA号</t>
   </si>
   <si>
     <t>Amazon Reference ID</t>
   </si>
   <si>
-    <t>派送方式</t>
-  </si>
-  <si>
     <t>快递单号</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>最早派送时间</t>
   </si>
   <si>
     <t>最晚派送时间</t>
-  </si>
-  <si>
-    <t>仓库代码</t>
   </si>
   <si>
     <t>红色颜色的字迹，为必填项</t>
@@ -1594,7 +1594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="1" max="1" width="15.5044247787611" customWidth="1"/>
@@ -1603,14 +1603,11 @@
     <col min="5" max="8" width="8.33628318584071" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="15.8761061946903" customWidth="1"/>
-    <col min="13" max="13" width="22.6283185840708" customWidth="1"/>
-    <col min="14" max="15" width="11.1681415929204" customWidth="1"/>
-    <col min="16" max="16" width="18.8318584070796" customWidth="1"/>
-    <col min="17" max="18" width="13.1681415929204" customWidth="1"/>
+    <col min="12" max="12" width="11.1681415929204" customWidth="1"/>
+    <col min="13" max="13" width="18.8318584070796" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="31" customFormat="1" ht="29" customHeight="1" spans="1:18">
+    <row r="1" s="31" customFormat="1" ht="29" customHeight="1" spans="1:13">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -1647,446 +1644,322 @@
       <c r="L1" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="33" t="s">
+      <c r="M1" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:13">
       <c r="A2" s="36"/>
       <c r="I2" s="36"/>
       <c r="J2" s="36"/>
       <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+      <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:13">
       <c r="A3" s="36"/>
       <c r="I3" s="36"/>
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
-      <c r="L3" s="36"/>
-      <c r="M3" s="36"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:18">
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+    <row r="4" spans="1:13">
+      <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:18">
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+    <row r="5" spans="1:13">
+      <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:18">
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+    <row r="6" spans="1:13">
+      <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:18">
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+    <row r="7" spans="1:13">
+      <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:18">
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+    <row r="8" spans="1:13">
+      <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:18">
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+    <row r="9" spans="1:13">
+      <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:18">
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+    <row r="10" spans="1:13">
+      <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:18">
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+    <row r="11" spans="1:13">
+      <c r="L11" s="2"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+    <row r="12" spans="1:13">
+      <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:18">
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+    <row r="13" spans="1:13">
+      <c r="L13" s="2"/>
     </row>
-    <row r="14" spans="1:18">
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+    <row r="14" spans="1:13">
+      <c r="L14" s="2"/>
     </row>
-    <row r="15" spans="1:18">
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+    <row r="15" spans="1:13">
+      <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:18">
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+    <row r="16" spans="1:13">
+      <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="14:15">
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+    <row r="17" spans="12:12">
+      <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="14:15">
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+    <row r="18" spans="12:12">
+      <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="14:15">
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+    <row r="19" spans="12:12">
+      <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="14:15">
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+    <row r="20" spans="12:12">
+      <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="14:15">
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+    <row r="21" spans="12:12">
+      <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="14:15">
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+    <row r="22" spans="12:12">
+      <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="14:15">
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+    <row r="23" spans="12:12">
+      <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="14:15">
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+    <row r="24" spans="12:12">
+      <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="14:15">
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+    <row r="25" spans="12:12">
+      <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="14:15">
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
+    <row r="26" spans="12:12">
+      <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="14:15">
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+    <row r="27" spans="12:12">
+      <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="14:15">
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+    <row r="28" spans="12:12">
+      <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="14:15">
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+    <row r="29" spans="12:12">
+      <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="14:15">
-      <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+    <row r="30" spans="12:12">
+      <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="14:15">
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+    <row r="31" spans="12:12">
+      <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="14:15">
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+    <row r="32" spans="12:12">
+      <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="14:15">
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+    <row r="33" spans="12:12">
+      <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="14:15">
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+    <row r="34" spans="12:12">
+      <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="14:15">
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+    <row r="35" spans="12:12">
+      <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="14:15">
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+    <row r="36" spans="12:12">
+      <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="14:15">
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+    <row r="37" spans="12:12">
+      <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="14:15">
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+    <row r="38" spans="12:12">
+      <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="14:15">
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+    <row r="39" spans="12:12">
+      <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="14:15">
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+    <row r="40" spans="12:12">
+      <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="14:15">
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+    <row r="41" spans="12:12">
+      <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="14:15">
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+    <row r="42" spans="12:12">
+      <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="14:15">
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+    <row r="43" spans="12:12">
+      <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="14:15">
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+    <row r="44" spans="12:12">
+      <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="14:15">
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+    <row r="45" spans="12:12">
+      <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="14:15">
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+    <row r="46" spans="12:12">
+      <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="14:15">
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+    <row r="47" spans="12:12">
+      <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="14:15">
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+    <row r="48" spans="12:12">
+      <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="14:15">
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+    <row r="49" spans="12:12">
+      <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="14:15">
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+    <row r="50" spans="12:12">
+      <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="14:15">
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+    <row r="51" spans="12:12">
+      <c r="L51" s="2"/>
     </row>
-    <row r="52" spans="14:15">
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+    <row r="52" spans="12:12">
+      <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="14:15">
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+    <row r="53" spans="12:12">
+      <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="14:15">
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+    <row r="54" spans="12:12">
+      <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="14:15">
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+    <row r="55" spans="12:12">
+      <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="14:15">
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+    <row r="56" spans="12:12">
+      <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="14:15">
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+    <row r="57" spans="12:12">
+      <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="14:15">
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+    <row r="58" spans="12:12">
+      <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="14:15">
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+    <row r="59" spans="12:12">
+      <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="14:15">
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+    <row r="60" spans="12:12">
+      <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="14:15">
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+    <row r="61" spans="12:12">
+      <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="14:15">
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+    <row r="62" spans="12:12">
+      <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="14:15">
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+    <row r="63" spans="12:12">
+      <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="14:15">
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+    <row r="64" spans="12:12">
+      <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="14:15">
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+    <row r="65" spans="12:12">
+      <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="14:15">
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+    <row r="66" spans="12:12">
+      <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="14:15">
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+    <row r="67" spans="12:12">
+      <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="14:15">
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+    <row r="68" spans="12:12">
+      <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="14:15">
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+    <row r="69" spans="12:12">
+      <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="14:15">
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+    <row r="70" spans="12:12">
+      <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="14:15">
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+    <row r="71" spans="12:12">
+      <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="14:15">
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+    <row r="72" spans="12:12">
+      <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="14:15">
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
+    <row r="73" spans="12:12">
+      <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="14:15">
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+    <row r="74" spans="12:12">
+      <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="14:15">
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+    <row r="75" spans="12:12">
+      <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="14:15">
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
+    <row r="76" spans="12:12">
+      <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="14:15">
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+    <row r="77" spans="12:12">
+      <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="14:15">
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+    <row r="78" spans="12:12">
+      <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="14:15">
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+    <row r="79" spans="12:12">
+      <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="14:15">
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+    <row r="80" spans="12:12">
+      <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="14:15">
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+    <row r="81" spans="12:12">
+      <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="14:15">
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+    <row r="82" spans="12:12">
+      <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="14:15">
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+    <row r="83" spans="12:12">
+      <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="14:15">
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+    <row r="84" spans="12:12">
+      <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="14:15">
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
+    <row r="85" spans="12:12">
+      <c r="L85" s="2"/>
     </row>
-    <row r="86" spans="14:15">
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+    <row r="86" spans="12:12">
+      <c r="L86" s="2"/>
     </row>
-    <row r="87" spans="14:15">
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+    <row r="87" spans="12:12">
+      <c r="L87" s="2"/>
     </row>
-    <row r="88" spans="14:15">
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
+    <row r="88" spans="12:12">
+      <c r="L88" s="2"/>
     </row>
-    <row r="89" spans="14:15">
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+    <row r="89" spans="12:12">
+      <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="14:15">
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+    <row r="90" spans="12:12">
+      <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="14:15">
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+    <row r="91" spans="12:12">
+      <c r="L91" s="2"/>
     </row>
-    <row r="92" spans="14:15">
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+    <row r="92" spans="12:12">
+      <c r="L92" s="2"/>
     </row>
-    <row r="93" spans="14:15">
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+    <row r="93" spans="12:12">
+      <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="14:15">
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+    <row r="94" spans="12:12">
+      <c r="L94" s="2"/>
     </row>
-    <row r="95" spans="14:15">
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
+    <row r="95" spans="12:12">
+      <c r="L95" s="2"/>
     </row>
-    <row r="96" spans="14:15">
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+    <row r="96" spans="12:12">
+      <c r="L96" s="2"/>
     </row>
-    <row r="97" spans="14:15">
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+    <row r="97" spans="12:12">
+      <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="14:15">
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+    <row r="98" spans="12:12">
+      <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="14:15">
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
+    <row r="99" spans="12:12">
+      <c r="L99" s="2"/>
     </row>
-    <row r="100" spans="14:15">
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+    <row r="100" spans="12:12">
+      <c r="L100" s="2"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange algorithmName="SHA-512" hashValue="UzA0nOFUeaFtULQSIT4958zhoYyTmirahG2yNfR1IG/8l49DY8qF3CYXVXIUJIJtfHaTg0AH2Mgy69FLGfFI8g==" saltValue="s1fm+kLliY0bj7VgCAWACg==" spinCount="100000" sqref="A1" name="区域1"/>
-    <protectedRange sqref="O1" name="区域1_1"/>
   </protectedRanges>
-  <dataValidations count="3">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="录入提示" error="不能修改标题" sqref="O1">
-      <formula1>"快递单号"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:O100">
-      <formula1>"卡车派送,UPS,FEDEX,DHL,DPD,TNT,客户自提,仓储上架,暂扣留仓(HOLD),整柜直送,大货中转,亚马逊自提,UPS LTL,LTL,PICKUP BY CNEE,STORED IN W.H.,PARCEL WITH LABEL,PARCEL WITHOUT LABEL,FTL,FCL"</formula1>
-    </dataValidation>
-    <dataValidation type="date" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="日期格式：YYYY-MM-DD" prompt="例 2025-08-21" sqref="Q2:R100">
-      <formula1>36526</formula1>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L$1:L$1048576">
+      <formula1>"自提,自发"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2146,31 +2019,31 @@
         <v>7</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>10</v>
       </c>
       <c r="K1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="N1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" s="12" t="s">
-        <v>15</v>
-      </c>
       <c r="P1" s="13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q1" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" ht="51" customHeight="1" spans="1:17">
@@ -35194,7 +35067,6 @@
 <allowEditUser xmlns="https://web.wps.cn/et/2018/main" xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main" hasInvisiblePropRange="0">
   <rangeList sheetStid="2" master="" otherUserPermission="visible">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
-    <arrUserId title="区域1_1" rangeCreator="" othersAccessPermission="edit"/>
   </rangeList>
   <rangeList sheetStid="3" master="" otherUserPermission="visible">
     <arrUserId title="区域1" rangeCreator="" othersAccessPermission="edit"/>
